--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>40001 LUIS H. BOURONCLE</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-16.39186</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-71.53059</v>
-      </c>
-      <c r="I2" t="n">
-        <v>451</v>
-      </c>
-      <c r="J2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-16.39186</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-71.53059</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>40002 AL AIRE LIBRE</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-16.40718</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-71.53606000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>343</v>
-      </c>
-      <c r="J3" t="n">
-        <v>21</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-16.40718</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-71.53606</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-16.428617</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-71.557917</v>
-      </c>
-      <c r="I4" t="n">
-        <v>557</v>
-      </c>
-      <c r="J4" t="n">
-        <v>39</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-16.428617</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-71.557917</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>40025 SANTA DOROTEA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-16.41802</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-71.53951000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>320</v>
-      </c>
-      <c r="J5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-16.41802</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-71.53951</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>40165 SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-16.40489</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-71.55067</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1075</v>
-      </c>
-      <c r="J6" t="n">
-        <v>56</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-16.40489</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-71.55067</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>41008 MANUEL MUÑOZ NAJAR</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-16.39941</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-71.52401</v>
-      </c>
-      <c r="I7" t="n">
-        <v>796</v>
-      </c>
-      <c r="J7" t="n">
-        <v>53</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-16.39941</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-71.52401</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>41014 FORTUNATA GUTIERREZ DE BERNED / 41014 FORTUNATA GUTIERREZ DE BERNEDO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-16.40433</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-71.5397</v>
-      </c>
-      <c r="I8" t="n">
-        <v>263</v>
-      </c>
-      <c r="J8" t="n">
-        <v>16</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-16.40433</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-71.5397</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>GRAN PACIFICADOR LINUS PAULING</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-16.40312</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-71.53783</v>
-      </c>
-      <c r="I9" t="n">
-        <v>387</v>
-      </c>
-      <c r="J9" t="n">
-        <v>26</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-16.40312</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-71.53783</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>41019 REPUBLICA DE VENEZUELA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-16.396551</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-71.532955</v>
-      </c>
-      <c r="I10" t="n">
-        <v>230</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-16.396551</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-71.532955</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>AREQUIPA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-16.39225</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-71.5295</v>
-      </c>
-      <c r="I11" t="n">
-        <v>892</v>
-      </c>
-      <c r="J11" t="n">
-        <v>66</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-16.39225</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-71.5295</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>INDEPENDENCIA AMERICANA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-16.40821</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-71.53191</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1293</v>
-      </c>
-      <c r="J12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-16.40821</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-71.53191</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>JUANA CERVANTES DE BOLOGNESI</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-16.40586</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-71.54491</v>
-      </c>
-      <c r="I13" t="n">
-        <v>760</v>
-      </c>
-      <c r="J13" t="n">
-        <v>60</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-16.40586</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-71.54491</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-16.396228</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-71.530154</v>
-      </c>
-      <c r="I14" t="n">
-        <v>729</v>
-      </c>
-      <c r="J14" t="n">
-        <v>49</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-16.396228</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-71.530154</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>40020 ESCUELA ECOLOGICA URBANA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-16.39087</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-71.53400999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>336</v>
-      </c>
-      <c r="J15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-16.39087</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-71.53401</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-16.400025</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-71.527225</v>
-      </c>
-      <c r="I16" t="n">
-        <v>265</v>
-      </c>
-      <c r="J16" t="n">
-        <v>23</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-16.400025</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-71.527225</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>ESCLAVAS DEL SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-16.40389</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-71.55092</v>
-      </c>
-      <c r="I17" t="n">
-        <v>811</v>
-      </c>
-      <c r="J17" t="n">
-        <v>54</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-16.40389</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-71.55092</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>LA RECOLETA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-16.3951</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-71.54235</v>
-      </c>
-      <c r="I18" t="n">
-        <v>602</v>
-      </c>
-      <c r="J18" t="n">
-        <v>46</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-16.3951</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-71.54235</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-16.396517</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-71.52652500000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>375</v>
-      </c>
-      <c r="J19" t="n">
-        <v>26</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-16.396517</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-71.526525</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>MARIA INMACULADA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-16.4092</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-71.5429</v>
-      </c>
-      <c r="I20" t="n">
-        <v>72</v>
-      </c>
-      <c r="J20" t="n">
-        <v>8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-16.4092</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-71.5429</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-16.4048</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-71.547911</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1128</v>
-      </c>
-      <c r="J21" t="n">
-        <v>63</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-16.4048</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-71.547911</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>SALESIANOS DON BOSCO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-16.39716</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-71.52858999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>734</v>
-      </c>
-      <c r="J22" t="n">
-        <v>38</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-16.39716</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-71.52859</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>SAN JERONIMO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-16.408</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-71.54900000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>794</v>
-      </c>
-      <c r="J23" t="n">
-        <v>60</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-16.408</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-71.549</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SANTA ROSA DE VITERBO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-16.3965</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-71.54371</v>
-      </c>
-      <c r="I24" t="n">
-        <v>972</v>
-      </c>
-      <c r="J24" t="n">
-        <v>56</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-16.3965</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-71.54371</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>COLEGIO ANGLO AMERICANO PRESCOTT</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-16.4288</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-71.560733</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1339</v>
-      </c>
-      <c r="J25" t="n">
-        <v>178</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-16.4288</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-71.560733</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>BLAS PASCAL</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-16.39964</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-71.52567000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>339</v>
-      </c>
-      <c r="J26" t="n">
-        <v>25</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-16.39964</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-71.52567</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>CLARET</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-16.40216</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-71.54154</v>
-      </c>
-      <c r="I27" t="n">
-        <v>417</v>
-      </c>
-      <c r="J27" t="n">
-        <v>44</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-16.40216</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-71.54154</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>PADRE DAMIAN DE LOS SAGRADOS CORAZONES</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-16.404478</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-71.536779</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J28" t="n">
-        <v>50</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-16.404478</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-71.536779</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>FRANCISCO ROJAS SCHOOL</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-16.40801</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-71.52882</v>
-      </c>
-      <c r="I29" t="n">
-        <v>246</v>
-      </c>
-      <c r="J29" t="n">
-        <v>19</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-16.40801</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-71.52882</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>DE LA SALLE</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-16.4004</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-71.52506</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1471</v>
-      </c>
-      <c r="J30" t="n">
-        <v>78</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-16.4004</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-71.52506</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>ORLEANS GOLEMAN</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-16.404297</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-71.539447</v>
-      </c>
-      <c r="I31" t="n">
-        <v>505</v>
-      </c>
-      <c r="J31" t="n">
-        <v>33</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-16.404297</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-71.539447</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>NUESTRA SEÑORA DEL PILAR</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-16.4116</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-71.533817</v>
-      </c>
-      <c r="I32" t="n">
-        <v>885</v>
-      </c>
-      <c r="J32" t="n">
-        <v>72</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-16.4116</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-71.533817</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-16.40364</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-71.53111</v>
-      </c>
-      <c r="I33" t="n">
-        <v>246</v>
-      </c>
-      <c r="J33" t="n">
-        <v>22</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-16.40364</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-71.53111</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>ALAS PERUANAS</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-16.4116</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-71.5248</v>
-      </c>
-      <c r="I34" t="n">
-        <v>248</v>
-      </c>
-      <c r="J34" t="n">
-        <v>29</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-16.4116</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-71.5248</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-16.40374</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-71.52843</v>
-      </c>
-      <c r="I35" t="n">
-        <v>343</v>
-      </c>
-      <c r="J35" t="n">
-        <v>30</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-16.40374</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-71.52843</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>DE LOS SAGRADOS CORAZONES</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-16.4278</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-71.55936699999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>749</v>
-      </c>
-      <c r="J36" t="n">
-        <v>53</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-16.4278</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-71.559367</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>SAN JOSE DE AREQUIPA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-16.424333</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-71.55546699999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1128</v>
-      </c>
-      <c r="J37" t="n">
-        <v>100</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-16.424333</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-71.555467</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SAN PEDRO PASCUAL</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-16.4019</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-71.539333</v>
-      </c>
-      <c r="I38" t="n">
-        <v>904</v>
-      </c>
-      <c r="J38" t="n">
-        <v>49</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-16.4019</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-71.539333</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>ALEXANDER FLEMING</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-16.4114</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-71.52775</v>
-      </c>
-      <c r="I39" t="n">
-        <v>890</v>
-      </c>
-      <c r="J39" t="n">
-        <v>44</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-16.4114</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-71.52775</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>40029 LUDWING VAN BEETHOVEN</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-16.36331</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-71.5218</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1379</v>
-      </c>
-      <c r="J40" t="n">
-        <v>71</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-16.36331</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-71.5218</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>LORD BYRON</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-16.39106</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-71.55094</v>
-      </c>
-      <c r="I41" t="n">
-        <v>773</v>
-      </c>
-      <c r="J41" t="n">
-        <v>54</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-16.39106</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-71.55094</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>40068</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-16.477495</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-71.819639</v>
-      </c>
-      <c r="I42" t="n">
-        <v>316</v>
-      </c>
-      <c r="J42" t="n">
-        <v>17</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-16.477495</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-71.819639</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>40326 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-16.685581</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-71.885351</v>
-      </c>
-      <c r="I43" t="n">
-        <v>460</v>
-      </c>
-      <c r="J43" t="n">
-        <v>29</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-16.685581</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-71.885351</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>RAFAEL LOAYZA GUEVARA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-16.40985</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-71.51345000000001</v>
-      </c>
-      <c r="I44" t="n">
-        <v>963</v>
-      </c>
-      <c r="J44" t="n">
-        <v>75</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-16.40985</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-71.51345</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>40148 GERARDO IQUIRA PIZARRO</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-16.38431</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-71.51118</v>
-      </c>
-      <c r="I45" t="n">
-        <v>206</v>
-      </c>
-      <c r="J45" t="n">
-        <v>13</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-16.38431</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-71.51118</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>41037 JOSE GALVEZ</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-16.39426</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-71.51967</v>
-      </c>
-      <c r="I46" t="n">
-        <v>445</v>
-      </c>
-      <c r="J46" t="n">
-        <v>33</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-16.39426</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-71.51967</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>MERE DU CHRIST</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-16.389957</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-71.516121</v>
-      </c>
-      <c r="I47" t="n">
-        <v>278</v>
-      </c>
-      <c r="J47" t="n">
-        <v>19</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-16.389957</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-71.516121</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>40160 OBDULIO BARRIGA VIZCARRA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-16.487072</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-71.46969799999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>217</v>
-      </c>
-      <c r="J48" t="n">
-        <v>17</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-16.487072</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-71.469698</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>JESUS NAZARENO</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-16.432678</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-71.503353</v>
-      </c>
-      <c r="I49" t="n">
-        <v>290</v>
-      </c>
-      <c r="J49" t="n">
-        <v>18</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-16.432678</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-71.503353</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>40195</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-16.444211</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-71.483519</v>
-      </c>
-      <c r="I50" t="n">
-        <v>31</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-16.444211</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-71.483519</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>40079 VICTOR NUÑEZ VALENCIA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-16.41213</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-71.57861</v>
-      </c>
-      <c r="I51" t="n">
-        <v>498</v>
-      </c>
-      <c r="J51" t="n">
-        <v>28</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-16.41213</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-71.57861</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>40676 LA MANSION DE SOCABAYA</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-16.46703</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-71.55127</v>
-      </c>
-      <c r="I52" t="n">
-        <v>327</v>
-      </c>
-      <c r="J52" t="n">
-        <v>19</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-16.46703</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-71.55127</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>FRANCISCO MOSTAJO</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-16.4464</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-71.58795000000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>416</v>
-      </c>
-      <c r="J53" t="n">
-        <v>24</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-16.4464</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-71.58795</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>DE CIENCIAS DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-16.44699</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-71.59529999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>293</v>
-      </c>
-      <c r="J54" t="n">
-        <v>23</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-16.44699</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-71.5953</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-16.44913</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-71.58953</v>
-      </c>
-      <c r="I55" t="n">
-        <v>220</v>
-      </c>
-      <c r="J55" t="n">
-        <v>13</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-16.44913</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-71.58953</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>40088 REYNO DE BELGICA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-16.424876</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-71.673171</v>
-      </c>
-      <c r="I56" t="n">
-        <v>281</v>
-      </c>
-      <c r="J56" t="n">
-        <v>15</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-16.424876</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-71.673171</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>40091 ALMA MATER DE CONGATA</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-16.44535</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-71.620925</v>
-      </c>
-      <c r="I57" t="n">
-        <v>443</v>
-      </c>
-      <c r="J57" t="n">
-        <v>27</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-16.44535</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-71.620925</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>INTERNACIONAL ALBERT L. LEHNINGER</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-16.39996</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-71.53894</v>
-      </c>
-      <c r="I58" t="n">
-        <v>245</v>
-      </c>
-      <c r="J58" t="n">
-        <v>22</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-16.39996</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-71.53894</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>CHAVEZ DE LA ROSA</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-16.398092</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-71.52585000000001</v>
-      </c>
-      <c r="I59" t="n">
-        <v>235</v>
-      </c>
-      <c r="J59" t="n">
-        <v>12</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-16.398092</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-71.52585</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>STANFORD</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-16.39713</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-71.542604</v>
-      </c>
-      <c r="I60" t="n">
-        <v>284</v>
-      </c>
-      <c r="J60" t="n">
-        <v>20</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-16.39713</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-71.542604</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>HEFZIBA</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-16.404433</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-71.5625</v>
-      </c>
-      <c r="I61" t="n">
-        <v>211</v>
-      </c>
-      <c r="J61" t="n">
-        <v>14</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-16.404433</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-71.5625</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>ARCANGEL SAN MIGUEL</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-16.44449</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-71.506771</v>
-      </c>
-      <c r="I62" t="n">
-        <v>272</v>
-      </c>
-      <c r="J62" t="n">
-        <v>17</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-16.44449</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-71.506771</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>SEYMOUR BRUNER</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-16.398843</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-71.524658</v>
-      </c>
-      <c r="I63" t="n">
-        <v>218</v>
-      </c>
-      <c r="J63" t="n">
-        <v>16</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-16.398843</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-71.524658</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>VIRGEN DEL CARMEN MILAGROSA</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-16.4055</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-71.5397</v>
-      </c>
-      <c r="I64" t="n">
-        <v>47</v>
-      </c>
-      <c r="J64" t="n">
-        <v>4</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-16.4055</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-71.5397</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>MY ANGEL SCHOOL</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-16.40948</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-71.54321</v>
-      </c>
-      <c r="I65" t="n">
-        <v>68</v>
-      </c>
-      <c r="J65" t="n">
-        <v>11</v>
-      </c>
-      <c r="K65" t="n">
-        <v>1</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-16.40948</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-71.54321</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>EBENEZER</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-16.398289</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-71.52882200000001</v>
-      </c>
-      <c r="I66" t="n">
-        <v>242</v>
-      </c>
-      <c r="J66" t="n">
-        <v>17</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-16.398289</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-71.528822</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>LICEE JEAN BAPTISTE LAMARCK</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-16.40767</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-71.54007</v>
-      </c>
-      <c r="I67" t="n">
-        <v>304</v>
-      </c>
-      <c r="J67" t="n">
-        <v>25</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-16.40767</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-71.54007</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>JOYCE</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-16.400733</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-71.532033</v>
-      </c>
-      <c r="I68" t="n">
-        <v>530</v>
-      </c>
-      <c r="J68" t="n">
-        <v>29</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-16.400733</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-71.532033</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>SANTA LUCIA</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-16.4037</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-71.5393</v>
-      </c>
-      <c r="I69" t="n">
-        <v>304</v>
-      </c>
-      <c r="J69" t="n">
-        <v>22</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-16.4037</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-71.5393</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>PANAMERICANO</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-16.4025</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-71.52160000000001</v>
-      </c>
-      <c r="I70" t="n">
-        <v>342</v>
-      </c>
-      <c r="J70" t="n">
-        <v>32</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-16.4025</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-71.5216</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>LUCIEN FREUD</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-16.39927</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-71.52573</v>
-      </c>
-      <c r="I71" t="n">
-        <v>667</v>
-      </c>
-      <c r="J71" t="n">
-        <v>32</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-16.39927</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-71.52573</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>TRILCE AREQUIPA</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-16.39957</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-71.54680999999999</v>
-      </c>
-      <c r="I72" t="n">
-        <v>273</v>
-      </c>
-      <c r="J72" t="n">
-        <v>14</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-16.39957</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-71.54681</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>40143 / HONORIO DELGADO ESPINOZA</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-16.41849</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-71.53863</v>
-      </c>
-      <c r="I73" t="n">
-        <v>310</v>
-      </c>
-      <c r="J73" t="n">
-        <v>18</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-16.41849</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-71.53863</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>LA CANTUTA DE AREQUIPA</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-16.395345</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-71.527984</v>
-      </c>
-      <c r="I74" t="n">
-        <v>420</v>
-      </c>
-      <c r="J74" t="n">
-        <v>31</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-16.395345</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-71.527984</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>JOULE - SOCABAYA</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-16.485565</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-71.50153400000001</v>
-      </c>
-      <c r="I75" t="n">
-        <v>277</v>
-      </c>
-      <c r="J75" t="n">
-        <v>19</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-16.485565</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-71.501534</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>REICH LA PERLA</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-16.40715</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-71.52979999999999</v>
-      </c>
-      <c r="I76" t="n">
-        <v>216</v>
-      </c>
-      <c r="J76" t="n">
-        <v>16</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-16.40715</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-71.5298</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>ADVENTISTA GENERAL JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-16.4044</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-71.54078</v>
-      </c>
-      <c r="I77" t="n">
-        <v>347</v>
-      </c>
-      <c r="J77" t="n">
-        <v>25</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-16.4044</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-71.54078</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>ANDENES DE CHILINA</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-16.372903</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-71.5292</v>
-      </c>
-      <c r="I78" t="n">
-        <v>655</v>
-      </c>
-      <c r="J78" t="n">
-        <v>37</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-16.372903</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-71.5292</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>NUCLEO JOULE</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-16.39788</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-71.53234999999999</v>
-      </c>
-      <c r="I79" t="n">
-        <v>73</v>
-      </c>
-      <c r="J79" t="n">
-        <v>9</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-16.39788</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-71.53235</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>SAGRADO CORAZON</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-16.3704</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-71.55944</v>
-      </c>
-      <c r="I80" t="n">
-        <v>683</v>
-      </c>
-      <c r="J80" t="n">
-        <v>66</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-16.3704</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-71.55944</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>JESUS MARIA - SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-16.39327</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-71.5322</v>
-      </c>
-      <c r="I81" t="n">
-        <v>231</v>
-      </c>
-      <c r="J81" t="n">
-        <v>20</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-16.39327</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-71.5322</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>TALENT SCHOOL</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-16.40145</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-71.531233</v>
-      </c>
-      <c r="I82" t="n">
-        <v>400</v>
-      </c>
-      <c r="J82" t="n">
-        <v>20</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-16.40145</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-71.531233</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>COLEGIO MAYOR MENDEL</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-16.3925</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-71.5329</v>
-      </c>
-      <c r="I83" t="n">
-        <v>737</v>
-      </c>
-      <c r="J83" t="n">
-        <v>34</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-16.3925</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-71.5329</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>MENDEL UMACOLLO</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-16.406</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-71.547067</v>
-      </c>
-      <c r="I84" t="n">
-        <v>408</v>
-      </c>
-      <c r="J84" t="n">
-        <v>34</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-16.406</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-71.547067</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>FARADAY</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-16.39674</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-71.53745000000001</v>
-      </c>
-      <c r="I85" t="n">
-        <v>444</v>
-      </c>
-      <c r="J85" t="n">
-        <v>32</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-16.39674</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-71.53745</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>FARADAY</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-16.39768</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-71.53162</v>
-      </c>
-      <c r="I86" t="n">
-        <v>189</v>
-      </c>
-      <c r="J86" t="n">
-        <v>6</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-16.39768</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-71.53162</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>BRYCE S.A.C.</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-16.39673</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-71.52612000000001</v>
-      </c>
-      <c r="I87" t="n">
-        <v>367</v>
-      </c>
-      <c r="J87" t="n">
-        <v>25</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-16.39673</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-71.52612</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>SIR ALEXANDER FLEMING</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-16.39652</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-71.53239600000001</v>
-      </c>
-      <c r="I88" t="n">
-        <v>431</v>
-      </c>
-      <c r="J88" t="n">
-        <v>25</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-16.39652</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-71.532396</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>55262</t>
+          <t>57138</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40001 LUIS H. BOURONCLE</t>
+          <t>SAN JOSE DE AREQUIPA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.39186</t>
+          <t>-16.424333</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.53059</t>
+          <t>-71.555467</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>540819</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40002 AL AIRE LIBRE</t>
+          <t>MY ANGEL SCHOOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.40718</t>
+          <t>-16.40948</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.53606</t>
+          <t>-71.54321</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>505260</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LOURDES</t>
+          <t>CHAVEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.428617</t>
+          <t>-16.398092</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.557917</t>
+          <t>-71.52585</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>55356</t>
+          <t>61852</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40025 SANTA DOROTEA</t>
+          <t>40148 GERARDO IQUIRA PIZARRO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.41802</t>
+          <t>-16.38431</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.53951</t>
+          <t>-71.51118</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>64681</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40165 SAN JUAN BAUTISTA DE LA SALLE</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.40489</t>
+          <t>-16.44913</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.55067</t>
+          <t>-71.58953</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>55455</t>
+          <t>529732</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41008 MANUEL MUÑOZ NAJAR</t>
+          <t>HEFZIBA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.39941</t>
+          <t>-16.404433</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.52401</t>
+          <t>-71.5625</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>55479</t>
+          <t>548146</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41014 FORTUNATA GUTIERREZ DE BERNED / 41014 FORTUNATA GUTIERREZ DE BERNEDO</t>
+          <t>TRILCE AREQUIPA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.40433</t>
+          <t>-16.39957</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.5397</t>
+          <t>-71.54681</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>55484</t>
+          <t>64723</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GRAN PACIFICADOR LINUS PAULING</t>
+          <t>40088 REYNO DE BELGICA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.40312</t>
+          <t>-16.424876</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.53783</t>
+          <t>-71.673171</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,27 +997,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55511</t>
+          <t>55356</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41019 REPUBLICA DE VENEZUELA</t>
+          <t>40025 SANTA DOROTEA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.396551</t>
+          <t>-16.41802</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.532955</t>
+          <t>-71.53951</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>55479</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>41014 FORTUNATA GUTIERREZ DE BERNED / 41014 FORTUNATA GUTIERREZ DE BERNEDO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.39225</t>
+          <t>-16.40433</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.5295</t>
+          <t>-71.5397</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55573</t>
+          <t>55511</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AMERICANA</t>
+          <t>41019 REPUBLICA DE VENEZUELA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.40821</t>
+          <t>-16.396551</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.53191</t>
+          <t>-71.532955</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>55592</t>
+          <t>540094</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JUANA CERVANTES DE BOLOGNESI</t>
+          <t>SEYMOUR BRUNER</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.40586</t>
+          <t>-16.398843</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.54491</t>
+          <t>-71.524658</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>55610</t>
+          <t>576573</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MICAELA BASTIDAS</t>
+          <t>REICH LA PERLA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.396228</t>
+          <t>-16.40715</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.530154</t>
+          <t>-71.5298</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>55634</t>
+          <t>60857</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40020 ESCUELA ECOLOGICA URBANA</t>
+          <t>40068</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.39087</t>
+          <t>-16.477495</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.53401</t>
+          <t>-71.819639</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55653</t>
+          <t>62413</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CORAZON DE MARIA</t>
+          <t>40160 OBDULIO BARRIGA VIZCARRA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.400025</t>
+          <t>-16.487072</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.527225</t>
+          <t>-71.469698</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>55686</t>
+          <t>533239</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ESCLAVAS DEL SAGRADO CORAZON DE JESUS</t>
+          <t>ARCANGEL SAN MIGUEL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.40389</t>
+          <t>-16.44449</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.55092</t>
+          <t>-71.506771</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>55691</t>
+          <t>541606</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LA RECOLETA</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.3951</t>
+          <t>-16.398289</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.54235</t>
+          <t>-71.528822</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>55912</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>COLEGIO ANGLO AMERICANO PRESCOTT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.396517</t>
+          <t>-16.4288</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.526525</t>
+          <t>-71.560733</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>55728</t>
+          <t>62842</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>JESUS NAZARENO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.4092</t>
+          <t>-16.432678</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.5429</t>
+          <t>-71.503353</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>55747</t>
+          <t>548226</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>40143 / HONORIO DELGADO ESPINOZA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.4048</t>
+          <t>-16.41849</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.547911</t>
+          <t>-71.53863</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>55766</t>
+          <t>55634</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SALESIANOS DON BOSCO</t>
+          <t>40020 ESCUELA ECOLOGICA URBANA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.39716</t>
+          <t>-16.39087</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.52859</t>
+          <t>-71.53401</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>336</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>55771</t>
+          <t>56290</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN JERONIMO</t>
+          <t>FRANCISCO ROJAS SCHOOL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.408</t>
+          <t>-16.40801</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.549</t>
+          <t>-71.52882</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>55785</t>
+          <t>62210</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE VITERBO</t>
+          <t>MERE DU CHRIST</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.3965</t>
+          <t>-16.389957</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.54371</t>
+          <t>-71.516121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>55912</t>
+          <t>64105</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>COLEGIO ANGLO AMERICANO PRESCOTT</t>
+          <t>40676 LA MANSION DE SOCABAYA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.4288</t>
+          <t>-16.46703</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.560733</t>
+          <t>-71.55127</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55974</t>
+          <t>551501</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BLAS PASCAL</t>
+          <t>JOULE - SOCABAYA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.39964</t>
+          <t>-16.485565</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.52567</t>
+          <t>-71.501534</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>56092</t>
+          <t>63484</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CLARET</t>
+          <t>40195</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.40216</t>
+          <t>-16.444211</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.54154</t>
+          <t>-71.483519</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>56172</t>
+          <t>526045</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PADRE DAMIAN DE LOS SAGRADOS CORAZONES</t>
+          <t>STANFORD</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.404478</t>
+          <t>-16.39713</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.536779</t>
+          <t>-71.542604</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>827637</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FRANCISCO ROJAS SCHOOL</t>
+          <t>JESUS MARIA - SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.40801</t>
+          <t>-16.39327</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.52882</t>
+          <t>-71.5322</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>56577</t>
+          <t>832945</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DE LA SALLE</t>
+          <t>TALENT SCHOOL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.4004</t>
+          <t>-16.40145</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.52506</t>
+          <t>-71.531233</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>56898</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ORLEANS GOLEMAN</t>
+          <t>40002 AL AIRE LIBRE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.404297</t>
+          <t>-16.40718</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.539447</t>
+          <t>-71.53606</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>56916</t>
+          <t>56921</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL PILAR</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-16.4116</t>
+          <t>-16.40364</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-71.533817</t>
+          <t>-71.53111</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,27 +2423,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>56921</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>INTERNACIONAL ALBERT L. LEHNINGER</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.40364</t>
+          <t>-16.39996</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.53111</t>
+          <t>-71.53894</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>546722</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ALAS PERUANAS</t>
+          <t>SANTA LUCIA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-16.4116</t>
+          <t>-16.4037</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-71.5248</t>
+          <t>-71.5393</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>57063</t>
+          <t>55653</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-16.40374</t>
+          <t>-16.400025</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-71.52843</t>
+          <t>-71.527225</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>57077</t>
+          <t>64676</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DE LOS SAGRADOS CORAZONES</t>
+          <t>DE CIENCIAS DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-16.4278</t>
+          <t>-16.44699</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-71.559367</t>
+          <t>-71.5953</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>64624</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAN JOSE DE AREQUIPA</t>
+          <t>FRANCISCO MOSTAJO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-16.424333</t>
+          <t>-16.4464</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-71.555467</t>
+          <t>-71.58795</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>416</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>55974</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SAN PEDRO PASCUAL</t>
+          <t>BLAS PASCAL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-16.4019</t>
+          <t>-16.39964</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-71.539333</t>
+          <t>-71.52567</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>339</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>57435</t>
+          <t>545609</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ALEXANDER FLEMING</t>
+          <t>LICEE JEAN BAPTISTE LAMARCK</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-16.4114</t>
+          <t>-16.40767</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-71.52775</t>
+          <t>-71.54007</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>57987</t>
+          <t>583088</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>40029 LUDWING VAN BEETHOVEN</t>
+          <t>ADVENTISTA GENERAL JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-16.36331</t>
+          <t>-16.4044</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-71.5218</t>
+          <t>-71.54078</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>347</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>59156</t>
+          <t>850760</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LORD BYRON</t>
+          <t>BRYCE S.A.C.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-16.39106</t>
+          <t>-16.39673</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-71.55094</t>
+          <t>-71.52612</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>60857</t>
+          <t>852783</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>SIR ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-16.477495</t>
+          <t>-16.39652</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-71.819639</t>
+          <t>-71.532396</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>431</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>60937</t>
+          <t>55484</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>40326 JUAN VELASCO ALVARADO</t>
+          <t>GRAN PACIFICADOR LINUS PAULING</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-16.685581</t>
+          <t>-16.40312</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-71.885351</t>
+          <t>-71.53783</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>387</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>55714</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RAFAEL LOAYZA GUEVARA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-16.40985</t>
+          <t>-16.396517</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-71.51345</t>
+          <t>-71.526525</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>61852</t>
+          <t>64742</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>40148 GERARDO IQUIRA PIZARRO</t>
+          <t>40091 ALMA MATER DE CONGATA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-16.38431</t>
+          <t>-16.44535</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-71.51118</t>
+          <t>-71.620925</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>61932</t>
+          <t>63554</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>41037 JOSE GALVEZ</t>
+          <t>40079 VICTOR NUÑEZ VALENCIA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-16.39426</t>
+          <t>-16.41213</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-71.51967</t>
+          <t>-71.57861</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>498</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>62210</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MERE DU CHRIST</t>
+          <t>ALAS PERUANAS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-16.389957</t>
+          <t>-16.4116</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-71.516121</t>
+          <t>-71.5248</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>62413</t>
+          <t>60937</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>40160 OBDULIO BARRIGA VIZCARRA</t>
+          <t>40326 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-16.487072</t>
+          <t>-16.685581</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-71.469698</t>
+          <t>-71.885351</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>460</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>62842</t>
+          <t>546576</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JESUS NAZARENO</t>
+          <t>JOYCE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-16.432678</t>
+          <t>-16.400733</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-71.503353</t>
+          <t>-71.532033</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>530</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>63484</t>
+          <t>55262</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>40195</t>
+          <t>40001 LUIS H. BOURONCLE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-16.444211</t>
+          <t>-16.39186</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-71.483519</t>
+          <t>-71.53059</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>451</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>63554</t>
+          <t>57063</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>40079 VICTOR NUÑEZ VALENCIA</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-16.41213</t>
+          <t>-16.40374</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-71.57861</t>
+          <t>-71.52843</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>64105</t>
+          <t>551148</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>40676 LA MANSION DE SOCABAYA</t>
+          <t>LA CANTUTA DE AREQUIPA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-16.46703</t>
+          <t>-16.395345</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-71.55127</t>
+          <t>-71.527984</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>420</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>547137</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FRANCISCO MOSTAJO</t>
+          <t>PANAMERICANO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-16.4464</t>
+          <t>-16.4025</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-71.58795</t>
+          <t>-71.5216</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>64676</t>
+          <t>547378</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DE CIENCIAS DIVINO NIÑO JESUS</t>
+          <t>LUCIEN FREUD</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-16.44699</t>
+          <t>-16.39927</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-71.5953</t>
+          <t>-71.52573</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>667</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>64681</t>
+          <t>849521</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>FARADAY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-16.44913</t>
+          <t>-16.39674</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-71.58953</t>
+          <t>-71.53745</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>444</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>56898</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>40088 REYNO DE BELGICA</t>
+          <t>ORLEANS GOLEMAN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-16.424876</t>
+          <t>-16.404297</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-71.673171</t>
+          <t>-71.539447</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>505</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>64742</t>
+          <t>61932</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>40091 ALMA MATER DE CONGATA</t>
+          <t>41037 JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-16.44535</t>
+          <t>-16.39426</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-71.620925</t>
+          <t>-71.51967</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>445</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>78785</t>
+          <t>833332</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ALBERT L. LEHNINGER</t>
+          <t>COLEGIO MAYOR MENDEL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-16.39996</t>
+          <t>-16.3925</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-71.53894</t>
+          <t>-71.5329</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>737</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>505260</t>
+          <t>839070</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CHAVEZ DE LA ROSA</t>
+          <t>MENDEL UMACOLLO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-16.398092</t>
+          <t>-16.406</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-71.52585</t>
+          <t>-71.547067</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>408</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>526045</t>
+          <t>625578</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>STANFORD</t>
+          <t>ANDENES DE CHILINA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-16.39713</t>
+          <t>-16.372903</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-71.542604</t>
+          <t>-71.5292</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>655</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>529732</t>
+          <t>55766</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HEFZIBA</t>
+          <t>SALESIANOS DON BOSCO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-16.404433</t>
+          <t>-16.39716</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-71.5625</t>
+          <t>-71.52859</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>734</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>533239</t>
+          <t>55342</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ARCANGEL SAN MIGUEL</t>
+          <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-16.44449</t>
+          <t>-16.428617</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-71.506771</t>
+          <t>-71.557917</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>557</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>540094</t>
+          <t>540169</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SEYMOUR BRUNER</t>
+          <t>VIRGEN DEL CARMEN MILAGROSA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-16.398843</t>
+          <t>-16.4055</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-71.524658</t>
+          <t>-71.5397</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,37 +4345,37 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>540169</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN MILAGROSA</t>
+          <t>CLARET</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-16.4055</t>
+          <t>-16.40216</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-71.5397</t>
+          <t>-71.54154</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>417</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4407,37 +4407,37 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>540819</t>
+          <t>57435</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MY ANGEL SCHOOL</t>
+          <t>ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-16.40948</t>
+          <t>-16.4114</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-71.54321</t>
+          <t>-71.52775</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>890</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>541606</t>
+          <t>55691</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>LA RECOLETA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-16.398289</t>
+          <t>-16.3951</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-71.528822</t>
+          <t>-71.54235</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>602</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>545609</t>
+          <t>55610</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LICEE JEAN BAPTISTE LAMARCK</t>
+          <t>MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-16.40767</t>
+          <t>-16.396228</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-71.54007</t>
+          <t>-71.530154</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>729</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>546576</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>JOYCE</t>
+          <t>SAN PEDRO PASCUAL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-16.400733</t>
+          <t>-16.4019</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-71.532033</t>
+          <t>-71.539333</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>904</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>546722</t>
+          <t>55573</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SANTA LUCIA</t>
+          <t>INDEPENDENCIA AMERICANA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-16.4037</t>
+          <t>-16.40821</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-71.5393</t>
+          <t>-71.53191</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>547137</t>
+          <t>56172</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PANAMERICANO</t>
+          <t>PADRE DAMIAN DE LOS SAGRADOS CORAZONES</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-16.4025</t>
+          <t>-16.404478</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-71.5216</t>
+          <t>-71.536779</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>547378</t>
+          <t>55455</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LUCIEN FREUD</t>
+          <t>41008 MANUEL MUÑOZ NAJAR</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-16.39927</t>
+          <t>-16.39941</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-71.52573</t>
+          <t>-71.52401</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>796</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>548146</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TRILCE AREQUIPA</t>
+          <t>DE LOS SAGRADOS CORAZONES</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-16.39957</t>
+          <t>-16.4278</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-71.54681</t>
+          <t>-71.559367</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>749</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,42 +4903,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>548226</t>
+          <t>55686</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>40143 / HONORIO DELGADO ESPINOZA</t>
+          <t>ESCLAVAS DEL SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-16.41849</t>
+          <t>-16.40389</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-71.53863</t>
+          <t>-71.55092</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>811</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>551148</t>
+          <t>59156</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LA CANTUTA DE AREQUIPA</t>
+          <t>LORD BYRON</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-16.395345</t>
+          <t>-16.39106</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-71.527984</t>
+          <t>-71.55094</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>773</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>551501</t>
+          <t>55441</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>JOULE - SOCABAYA</t>
+          <t>40165 SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-16.485565</t>
+          <t>-16.40489</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-71.501534</t>
+          <t>-71.55067</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>576573</t>
+          <t>55785</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>REICH LA PERLA</t>
+          <t>SANTA ROSA DE VITERBO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-16.40715</t>
+          <t>-16.3965</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-71.5298</t>
+          <t>-71.54371</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>972</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>583088</t>
+          <t>849880</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ADVENTISTA GENERAL JOSE DE SAN MARTIN</t>
+          <t>FARADAY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-16.4044</t>
+          <t>-16.39768</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-71.54078</t>
+          <t>-71.53162</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>189</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>625578</t>
+          <t>55592</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ANDENES DE CHILINA</t>
+          <t>JUANA CERVANTES DE BOLOGNESI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-16.372903</t>
+          <t>-16.40586</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-71.5292</t>
+          <t>-71.54491</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>760</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,37 +5275,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>764258</t>
+          <t>55771</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NUCLEO JOULE</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-16.39788</t>
+          <t>-16.408</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-71.53235</t>
+          <t>-71.549</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>794</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>826402</t>
+          <t>55747</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-16.3704</t>
+          <t>-16.4048</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-71.55944</t>
+          <t>-71.547911</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>827637</t>
+          <t>55525</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>JESUS MARIA - SAN MARTIN DE PORRES</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-16.39327</t>
+          <t>-16.39225</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-71.5322</t>
+          <t>-71.5295</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>892</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>832945</t>
+          <t>826402</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>TALENT SCHOOL</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-16.40145</t>
+          <t>-16.3704</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-71.531233</t>
+          <t>-71.55944</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>683</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>833332</t>
+          <t>57987</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>COLEGIO MAYOR MENDEL</t>
+          <t>40029 LUDWING VAN BEETHOVEN</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-16.3925</t>
+          <t>-16.36331</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-71.5329</t>
+          <t>-71.5218</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>839070</t>
+          <t>56916</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MENDEL UMACOLLO</t>
+          <t>NUESTRA SEÑORA DEL PILAR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-16.406</t>
+          <t>-16.4116</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-71.547067</t>
+          <t>-71.533817</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>885</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>849521</t>
+          <t>61381</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FARADAY</t>
+          <t>RAFAEL LOAYZA GUEVARA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-16.39674</t>
+          <t>-16.40985</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-71.53745</t>
+          <t>-71.51345</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>963</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>849880</t>
+          <t>56577</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FARADAY</t>
+          <t>DE LA SALLE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-16.39768</t>
+          <t>-16.4004</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-71.53162</t>
+          <t>-71.52506</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,37 +5771,37 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>850760</t>
+          <t>55728</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BRYCE S.A.C.</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-16.39673</t>
+          <t>-16.4092</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-71.52612</t>
+          <t>-71.5429</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5833,37 +5833,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>852783</t>
+          <t>764258</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SIR ALEXANDER FLEMING</t>
+          <t>NUCLEO JOULE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-16.39652</t>
+          <t>-16.39788</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-71.532396</t>
+          <t>-71.53235</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>852783</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAN JOSE DE AREQUIPA</t>
+          <t>SIR ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.424333</t>
+          <t>431</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.555467</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>-16.39652</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-71.532396</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>540819</t>
+          <t>850760</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MY ANGEL SCHOOL</t>
+          <t>BRYCE S.A.C.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.40948</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.54321</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-16.39673</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-71.52612</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>505260</t>
+          <t>849880</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CHAVEZ DE LA ROSA</t>
+          <t>FARADAY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.398092</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.52585</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-16.39768</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-71.53162</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>61852</t>
+          <t>849521</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40148 GERARDO IQUIRA PIZARRO</t>
+          <t>FARADAY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.38431</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.51118</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-16.39674</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-71.53745</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>64681</t>
+          <t>839070</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>MENDEL UMACOLLO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.44913</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.58953</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-16.406</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-71.547067</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>529732</t>
+          <t>833332</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HEFZIBA</t>
+          <t>COLEGIO MAYOR MENDEL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.404433</t>
+          <t>737</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.5625</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-16.3925</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.5329</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>548146</t>
+          <t>832945</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRILCE AREQUIPA</t>
+          <t>TALENT SCHOOL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.39957</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.54681</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-16.40145</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.531233</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>827637</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40088 REYNO DE BELGICA</t>
+          <t>JESUS MARIA - SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.424876</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.673171</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>-16.39327</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.5322</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55356</t>
+          <t>826402</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40025 SANTA DOROTEA</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.41802</t>
+          <t>683</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.53951</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>-16.3704</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.55944</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>55479</t>
+          <t>764258</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41014 FORTUNATA GUTIERREZ DE BERNED / 41014 FORTUNATA GUTIERREZ DE BERNEDO</t>
+          <t>NUCLEO JOULE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.40433</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.5397</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-16.39788</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.53235</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55511</t>
+          <t>625578</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41019 REPUBLICA DE VENEZUELA</t>
+          <t>ANDENES DE CHILINA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.396551</t>
+          <t>655</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.532955</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-16.372903</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.5292</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>540094</t>
+          <t>583088</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SEYMOUR BRUNER</t>
+          <t>ADVENTISTA GENERAL JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.398843</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.524658</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-16.4044</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.54078</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>-16.40715</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>-71.5298</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60857</t>
+          <t>551501</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>JOULE - SOCABAYA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.477495</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.819639</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>-16.485565</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.501534</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62413</t>
+          <t>551148</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40160 OBDULIO BARRIGA VIZCARRA</t>
+          <t>LA CANTUTA DE AREQUIPA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.487072</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.469698</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-16.395345</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.527984</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>533239</t>
+          <t>548226</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ARCANGEL SAN MIGUEL</t>
+          <t>40143 / HONORIO DELGADO ESPINOZA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.44449</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.506771</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-16.41849</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.53863</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>541606</t>
+          <t>548146</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>TRILCE AREQUIPA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.398289</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.528822</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-16.39957</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.54681</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>55912</t>
+          <t>547378</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>COLEGIO ANGLO AMERICANO PRESCOTT</t>
+          <t>LUCIEN FREUD</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.4288</t>
+          <t>667</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.560733</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>-16.39927</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>-71.52573</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>62842</t>
+          <t>547137</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JESUS NAZARENO</t>
+          <t>PANAMERICANO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.432678</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.503353</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-16.4025</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.5216</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>548226</t>
+          <t>546722</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40143 / HONORIO DELGADO ESPINOZA</t>
+          <t>SANTA LUCIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.41849</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.53863</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-16.4037</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.5393</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>55634</t>
+          <t>546576</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40020 ESCUELA ECOLOGICA URBANA</t>
+          <t>JOYCE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.39087</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.53401</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>-16.400733</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.532033</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>545609</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FRANCISCO ROJAS SCHOOL</t>
+          <t>LICEE JEAN BAPTISTE LAMARCK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.40801</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.52882</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-16.40767</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.54007</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>62210</t>
+          <t>541606</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MERE DU CHRIST</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.389957</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.516121</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-16.398289</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.528822</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>64105</t>
+          <t>540819</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>40676 LA MANSION DE SOCABAYA</t>
+          <t>MY ANGEL SCHOOL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.46703</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.55127</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-16.40948</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.54321</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>551501</t>
+          <t>540169</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JOULE - SOCABAYA</t>
+          <t>VIRGEN DEL CARMEN MILAGROSA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.485565</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.501534</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-16.4055</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.5397</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>63484</t>
+          <t>540094</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>40195</t>
+          <t>SEYMOUR BRUNER</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.444211</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.483519</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-16.398843</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-71.524658</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>526045</t>
+          <t>533239</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>STANFORD</t>
+          <t>ARCANGEL SAN MIGUEL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.39713</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.542604</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-16.44449</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.506771</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>827637</t>
+          <t>529732</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JESUS MARIA - SAN MARTIN DE PORRES</t>
+          <t>HEFZIBA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.39327</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.5322</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-16.404433</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.5625</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,37 +2237,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>832945</t>
+          <t>526045</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TALENT SCHOOL</t>
+          <t>STANFORD</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.40145</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.531233</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-16.39713</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.542604</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>505260</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>40002 AL AIRE LIBRE</t>
+          <t>CHAVEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.40718</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.53606</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-16.398092</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.52585</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>56921</t>
+          <t>078785</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>INTERNACIONAL ALBERT L. LEHNINGER</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-16.40364</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-71.53111</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-16.39996</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-71.53894</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>78785</t>
+          <t>064742</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ALBERT L. LEHNINGER</t>
+          <t>40091 ALMA MATER DE CONGATA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.39996</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.53894</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-16.44535</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-71.620925</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>546722</t>
+          <t>064723</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SANTA LUCIA</t>
+          <t>40088 REYNO DE BELGICA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-16.4037</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-71.5393</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-16.424876</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-71.673171</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>55653</t>
+          <t>064681</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CORAZON DE MARIA</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-16.400025</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-71.527225</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-16.44913</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-71.58953</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>64676</t>
+          <t>064676</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2619,22 +2619,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>-16.44699</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>-71.5953</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>064624</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2681,22 +2681,22 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>-16.4464</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>-71.58795</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>55974</t>
+          <t>064105</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BLAS PASCAL</t>
+          <t>40676 LA MANSION DE SOCABAYA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-16.39964</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-71.52567</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>-16.46703</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-71.55127</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>545609</t>
+          <t>063554</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LICEE JEAN BAPTISTE LAMARCK</t>
+          <t>40079 VICTOR NUÑEZ VALENCIA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-16.40767</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-71.54007</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-16.41213</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-71.57861</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>583088</t>
+          <t>063484</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ADVENTISTA GENERAL JOSE DE SAN MARTIN</t>
+          <t>40195</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-16.4044</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-71.54078</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-16.444211</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-71.483519</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>850760</t>
+          <t>062842</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BRYCE S.A.C.</t>
+          <t>JESUS NAZARENO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-16.39673</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-71.52612</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-16.432678</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-71.503353</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>852783</t>
+          <t>062413</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SIR ALEXANDER FLEMING</t>
+          <t>40160 OBDULIO BARRIGA VIZCARRA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-16.39652</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-71.532396</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>-16.487072</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-71.469698</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>55484</t>
+          <t>062210</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GRAN PACIFICADOR LINUS PAULING</t>
+          <t>MERE DU CHRIST</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-16.40312</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-71.53783</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>-16.389957</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.516121</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>061932</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>41037 JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-16.396517</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-71.526525</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>-16.39426</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.51967</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>64742</t>
+          <t>061852</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>40091 ALMA MATER DE CONGATA</t>
+          <t>40148 GERARDO IQUIRA PIZARRO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-16.44535</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-71.620925</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>-16.38431</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-71.51118</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>63554</t>
+          <t>061381</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>40079 VICTOR NUÑEZ VALENCIA</t>
+          <t>RAFAEL LOAYZA GUEVARA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-16.41213</t>
+          <t>963</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-71.57861</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>-16.40985</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-71.51345</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>060937</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ALAS PERUANAS</t>
+          <t>40326 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-16.4116</t>
+          <t>460</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-71.5248</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-16.685581</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-71.885351</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>60937</t>
+          <t>060857</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>40326 JUAN VELASCO ALVARADO</t>
+          <t>40068</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-16.685581</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-71.885351</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>-16.477495</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-71.819639</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>546576</t>
+          <t>059156</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JOYCE</t>
+          <t>LORD BYRON</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-16.400733</t>
+          <t>773</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-71.532033</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>-16.39106</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-71.55094</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>55262</t>
+          <t>057987</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>40001 LUIS H. BOURONCLE</t>
+          <t>40029 LUDWING VAN BEETHOVEN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-16.39186</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-71.53059</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>-16.36331</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-71.5218</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>57063</t>
+          <t>057435</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-16.40374</t>
+          <t>890</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-71.52843</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-16.4114</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-71.52775</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>551148</t>
+          <t>057176</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LA CANTUTA DE AREQUIPA</t>
+          <t>SAN PEDRO PASCUAL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-16.395345</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-71.527984</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>-16.4019</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-71.539333</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>547137</t>
+          <t>057138</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PANAMERICANO</t>
+          <t>SAN JOSE DE AREQUIPA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-16.4025</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-71.5216</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-16.424333</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-71.555467</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>547378</t>
+          <t>057077</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LUCIEN FREUD</t>
+          <t>DE LOS SAGRADOS CORAZONES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-16.39927</t>
+          <t>749</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-71.52573</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>-16.4278</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-71.559367</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>849521</t>
+          <t>057063</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FARADAY</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-16.39674</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-71.53745</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-16.40374</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-71.52843</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>56898</t>
+          <t>057044</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ORLEANS GOLEMAN</t>
+          <t>ALAS PERUANAS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-16.404297</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-71.539447</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>-16.4116</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-71.5248</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>61932</t>
+          <t>056921</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>41037 JOSE GALVEZ</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-16.39426</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-71.51967</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>-16.40364</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-71.53111</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>833332</t>
+          <t>056916</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>COLEGIO MAYOR MENDEL</t>
+          <t>NUESTRA SEÑORA DEL PILAR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-16.3925</t>
+          <t>885</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-71.5329</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>-16.4116</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-71.533817</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>839070</t>
+          <t>056898</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MENDEL UMACOLLO</t>
+          <t>ORLEANS GOLEMAN</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-16.406</t>
+          <t>505</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-71.547067</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>-16.404297</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-71.539447</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>625578</t>
+          <t>056577</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ANDENES DE CHILINA</t>
+          <t>DE LA SALLE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-16.372903</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-71.5292</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>-16.4004</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-71.52506</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>55766</t>
+          <t>056290</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SALESIANOS DON BOSCO</t>
+          <t>FRANCISCO ROJAS SCHOOL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-16.39716</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-71.52859</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>-16.40801</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-71.52882</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>056172</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LOURDES</t>
+          <t>PADRE DAMIAN DE LOS SAGRADOS CORAZONES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-16.428617</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-71.557917</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>-16.404478</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-71.536779</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>540169</t>
+          <t>056092</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN MILAGROSA</t>
+          <t>CLARET</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-16.4055</t>
+          <t>417</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-71.5397</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-16.40216</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-71.54154</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>56092</t>
+          <t>055974</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CLARET</t>
+          <t>BLAS PASCAL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-16.40216</t>
+          <t>339</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-71.54154</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>-16.39964</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-71.52567</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>57435</t>
+          <t>055912</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ALEXANDER FLEMING</t>
+          <t>COLEGIO ANGLO AMERICANO PRESCOTT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-16.4114</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-71.52775</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>-16.4288</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-71.560733</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>55691</t>
+          <t>055785</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LA RECOLETA</t>
+          <t>SANTA ROSA DE VITERBO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-16.3951</t>
+          <t>972</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-71.54235</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>-16.3965</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-71.54371</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>55610</t>
+          <t>055771</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MICAELA BASTIDAS</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-16.396228</t>
+          <t>794</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-71.530154</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>-16.408</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-71.549</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>055766</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SAN PEDRO PASCUAL</t>
+          <t>SALESIANOS DON BOSCO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-16.4019</t>
+          <t>734</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-71.539333</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>-16.39716</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-71.52859</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>55573</t>
+          <t>055747</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AMERICANA</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-16.40821</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-71.53191</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>-16.4048</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-71.547911</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,37 +4717,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>56172</t>
+          <t>055728</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PADRE DAMIAN DE LOS SAGRADOS CORAZONES</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-16.404478</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-71.536779</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>-16.4092</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-71.5429</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>55455</t>
+          <t>055714</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>41008 MANUEL MUÑOZ NAJAR</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-16.39941</t>
+          <t>375</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-71.52401</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>-16.396517</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-71.526525</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>57077</t>
+          <t>055691</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>DE LOS SAGRADOS CORAZONES</t>
+          <t>LA RECOLETA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-16.4278</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-71.559367</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>-16.3951</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-71.54235</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>55686</t>
+          <t>055686</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4913,22 +4913,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
           <t>-16.40389</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>-71.55092</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>811</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>59156</t>
+          <t>055653</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LORD BYRON</t>
+          <t>CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-16.39106</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-71.55094</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>-16.400025</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-71.527225</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>055634</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>40165 SAN JUAN BAUTISTA DE LA SALLE</t>
+          <t>40020 ESCUELA ECOLOGICA URBANA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-16.40489</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-71.55067</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>-16.39087</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-71.53401</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>55785</t>
+          <t>055610</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE VITERBO</t>
+          <t>MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-16.3965</t>
+          <t>729</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-71.54371</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>-16.396228</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-71.530154</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>849880</t>
+          <t>055592</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FARADAY</t>
+          <t>JUANA CERVANTES DE BOLOGNESI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-16.39768</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-71.53162</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>-16.40586</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-71.54491</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>55592</t>
+          <t>055573</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JUANA CERVANTES DE BOLOGNESI</t>
+          <t>INDEPENDENCIA AMERICANA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-16.40586</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-71.54491</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>-16.40821</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-71.53191</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>55771</t>
+          <t>055525</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SAN JERONIMO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-16.408</t>
+          <t>892</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-71.549</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>-16.39225</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-71.5295</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5337,37 +5337,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>55747</t>
+          <t>055511</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>41019 REPUBLICA DE VENEZUELA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-16.4048</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-71.547911</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>-16.396551</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-71.532955</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>055484</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>GRAN PACIFICADOR LINUS PAULING</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-16.39225</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-71.5295</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>-16.40312</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-71.53783</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>826402</t>
+          <t>055479</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>41014 FORTUNATA GUTIERREZ DE BERNED / 41014 FORTUNATA GUTIERREZ DE BERNEDO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-16.3704</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-71.55944</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>-16.40433</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-71.5397</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>57987</t>
+          <t>055455</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>40029 LUDWING VAN BEETHOVEN</t>
+          <t>41008 MANUEL MUÑOZ NAJAR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-16.36331</t>
+          <t>796</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-71.5218</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>-16.39941</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-71.52401</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>56916</t>
+          <t>055441</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL PILAR</t>
+          <t>40165 SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-16.4116</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-71.533817</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>-16.40489</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-71.55067</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>055356</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RAFAEL LOAYZA GUEVARA</t>
+          <t>40025 SANTA DOROTEA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-16.40985</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-71.51345</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>-16.41802</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-71.53951</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>56577</t>
+          <t>055342</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>DE LA SALLE</t>
+          <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-16.4004</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-71.52506</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>-16.428617</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-71.557917</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,37 +5771,37 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>55728</t>
+          <t>055276</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>40002 AL AIRE LIBRE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-16.4092</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-71.5429</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-16.40718</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-71.53606</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5833,37 +5833,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>764258</t>
+          <t>055262</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NUCLEO JOULE</t>
+          <t>40001 LUIS H. BOURONCLE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-16.39788</t>
+          <t>451</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-71.53235</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>-16.39186</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-71.53059</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-AREQUIPA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
